--- a/output/pdf_financials_xlsx/CSTR.xlsx
+++ b/output/pdf_financials_xlsx/CSTR.xlsx
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.249382</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.07620200000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.114881</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.050129</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.990383</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.18099</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.973876</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.196551</v>
       </c>
     </row>
     <row r="35">
@@ -1531,28 +1531,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.249382</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.07620200000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.114881</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7.050129</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.990383</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.18099</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.973876</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.196551</v>
       </c>
     </row>
     <row r="37">
@@ -1903,28 +1903,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.764294</v>
+        <v>3.514912</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.775514</v>
+        <v>0.699312</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.708323</v>
+        <v>3.593442</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>14.271804</v>
+        <v>7.221675</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.326576</v>
+        <v>0.336193</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.548309</v>
+        <v>0.367319</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.339859</v>
+        <v>0.365983</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.536132</v>
+        <v>0.339581</v>
       </c>
     </row>
     <row r="49">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">

--- a/output/pdf_financials_xlsx/CSTR.xlsx
+++ b/output/pdf_financials_xlsx/CSTR.xlsx
@@ -1301,22 +1301,22 @@
         <v>10.888345</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>7.196353</v>
+        <v>0.31317</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.588028</v>
+        <v>4.449863</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.300375</v>
+        <v>5.304122</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>4.663574</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>1.24749</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.950707</v>
       </c>
     </row>
     <row r="29">
@@ -1332,22 +1332,22 @@
         <v>-9.337364000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.060769</v>
+        <v>-1.822414</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.880984</v>
+        <v>0.980851</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-16.367721</v>
+        <v>-11.363974</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.613</v>
+        <v>-0.949426</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.648245</v>
+        <v>-3.400755</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.119977</v>
+        <v>-1.16927</v>
       </c>
     </row>
     <row r="30">
@@ -1372,19 +1372,19 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-60.75814181547854</v>
+        <v>20.68553110945911</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-301.9333248723661</v>
+        <v>-209.6298228435786</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-154.7641466644645</v>
+        <v>-26.17799834510171</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-223.2453494604548</v>
+        <v>-163.3310504081409</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-727.2623421532002</v>
+        <v>-401.1204078202133</v>
       </c>
     </row>
     <row r="31">
@@ -3559,22 +3559,22 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.31317</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>4.449863</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>5.304122</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>4.663574</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.24749</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.950707</v>
       </c>
     </row>
     <row r="101">
@@ -3934,19 +3934,19 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.014725</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.000835</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.91295</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>1.534724</v>
       </c>
     </row>
     <row r="113">
@@ -8566,7 +8566,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -9034,7 +9038,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -9238,7 +9246,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -9816,7 +9828,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -11110,7 +11126,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12906,7 +12922,11 @@
           <t>Depreciation - right-of-use- asset</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -15422,7 +15442,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -15439,19 +15463,19 @@
         </is>
       </c>
       <c r="H197" s="5" t="n">
-        <v>-0.325481</v>
+        <v>0.325481</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>-0.395097</v>
+        <v>0.395097</v>
       </c>
       <c r="J197" s="5" t="n">
-        <v>-0.435281</v>
+        <v>0.435281</v>
       </c>
       <c r="K197" s="5" t="n">
-        <v>-0.354611</v>
+        <v>0.354611</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>-0.41634</v>
+        <v>0.41634</v>
       </c>
     </row>
     <row r="198">
@@ -15470,7 +15494,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -15487,19 +15515,19 @@
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>-3.536354</v>
+        <v>3.536354</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>-4.909025</v>
+        <v>4.909025</v>
       </c>
       <c r="J198" s="5" t="n">
-        <v>-4.228293</v>
+        <v>4.228293</v>
       </c>
       <c r="K198" s="5" t="n">
-        <v>-0.892879</v>
+        <v>0.892879</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>-0.534367</v>
+        <v>0.534367</v>
       </c>
     </row>
     <row r="199">
@@ -17780,7 +17808,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -17799,10 +17827,10 @@
         </is>
       </c>
       <c r="H241" s="5" t="n">
-        <v>-0.588028</v>
+        <v>0.588028</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>-0.300375</v>
+        <v>0.300375</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -19012,7 +19040,11 @@
           <t>Depreciation - right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -19024,7 +19056,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>-0.31317</v>
+        <v>0.31317</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
